--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6961,6 +6961,48 @@
         <v>382.07</v>
       </c>
       <c r="E311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>409.78</v>
+      </c>
+      <c r="C312" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="D312" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>407.18</v>
+      </c>
+      <c r="C313" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="D313" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="E313" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -6977,7 +7019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10470,6 +10512,26 @@
       </c>
       <c r="B349" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.98</v>
       </c>
     </row>
   </sheetData>
@@ -10638,28 +10700,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01353497947738615</v>
+        <v>0.01871942435562964</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007338466749524652</v>
+        <v>0.001409444904098556</v>
       </c>
       <c r="M2" t="n">
-        <v>2.98444766431406</v>
+        <v>2.989595323185656</v>
       </c>
       <c r="N2" t="n">
-        <v>13.44016733603142</v>
+        <v>13.47159840454905</v>
       </c>
       <c r="O2" t="n">
-        <v>3.666083378215971</v>
+        <v>3.67036761163634</v>
       </c>
       <c r="P2" t="n">
-        <v>403.9992201236457</v>
+        <v>403.9415049675465</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10716,28 +10778,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1322603031112052</v>
+        <v>-0.133309553465305</v>
       </c>
       <c r="J3" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09240694926771975</v>
+        <v>0.09482864614787512</v>
       </c>
       <c r="M3" t="n">
-        <v>2.305311275022892</v>
+        <v>2.296252418092542</v>
       </c>
       <c r="N3" t="n">
-        <v>9.371425633372937</v>
+        <v>9.318164910664191</v>
       </c>
       <c r="O3" t="n">
-        <v>3.061278431206958</v>
+        <v>3.052566937949795</v>
       </c>
       <c r="P3" t="n">
-        <v>392.4029656155972</v>
+        <v>392.4145577451331</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10794,28 +10856,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3140079493072895</v>
+        <v>-0.3132661416202724</v>
       </c>
       <c r="J4" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3328898556885811</v>
+        <v>0.3347865644884299</v>
       </c>
       <c r="M4" t="n">
-        <v>2.418066931089225</v>
+        <v>2.406158631164678</v>
       </c>
       <c r="N4" t="n">
-        <v>10.77800487551994</v>
+        <v>10.71115986821803</v>
       </c>
       <c r="O4" t="n">
-        <v>3.282987187839749</v>
+        <v>3.2727908378352</v>
       </c>
       <c r="P4" t="n">
-        <v>392.3362206370281</v>
+        <v>392.3280282790697</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10853,7 +10915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19249,6 +19311,60 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.71444351549828,174.53773829169515</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.71456184539829,174.53862734541508</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.71437851200942,174.5394480392642</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.714466797595335,174.53774159009805</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.71457257175868,174.53863032047943</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.71437944947008,174.5394484353904</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7005,6 +7005,27 @@
       <c r="E313" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>408.26</v>
+      </c>
+      <c r="C314" t="n">
+        <v>388.37</v>
+      </c>
+      <c r="D314" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10532,6 +10553,16 @@
       </c>
       <c r="B351" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -10700,28 +10731,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01871942435562964</v>
+        <v>0.02111121459195811</v>
       </c>
       <c r="J2" t="n">
+        <v>313</v>
+      </c>
+      <c r="K2" t="n">
         <v>312</v>
       </c>
-      <c r="K2" t="n">
-        <v>311</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.001409444904098556</v>
+        <v>0.001797870150503145</v>
       </c>
       <c r="M2" t="n">
-        <v>2.989595323185656</v>
+        <v>2.991123089805276</v>
       </c>
       <c r="N2" t="n">
-        <v>13.47159840454905</v>
+        <v>13.47450627697258</v>
       </c>
       <c r="O2" t="n">
-        <v>3.67036761163634</v>
+        <v>3.670763718488645</v>
       </c>
       <c r="P2" t="n">
-        <v>403.9415049675465</v>
+        <v>403.9147871301482</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10778,28 +10809,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.133309553465305</v>
+        <v>-0.1335916572280643</v>
       </c>
       <c r="J3" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09482864614787512</v>
+        <v>0.09576456398569777</v>
       </c>
       <c r="M3" t="n">
-        <v>2.296252418092542</v>
+        <v>2.290438717343562</v>
       </c>
       <c r="N3" t="n">
-        <v>9.318164910664191</v>
+        <v>9.289047163557852</v>
       </c>
       <c r="O3" t="n">
-        <v>3.052566937949795</v>
+        <v>3.047793819069435</v>
       </c>
       <c r="P3" t="n">
-        <v>392.4145577451331</v>
+        <v>392.4176837123178</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10856,28 +10887,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3132661416202724</v>
+        <v>-0.312038668063672</v>
       </c>
       <c r="J4" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3347865644884299</v>
+        <v>0.3342721619426974</v>
       </c>
       <c r="M4" t="n">
-        <v>2.406158631164678</v>
+        <v>2.404353624526213</v>
       </c>
       <c r="N4" t="n">
-        <v>10.71115986821803</v>
+        <v>10.68929701740653</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2727908378352</v>
+        <v>3.269449038814725</v>
       </c>
       <c r="P4" t="n">
-        <v>392.3280282790697</v>
+        <v>392.3144267516726</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10915,7 +10946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19365,6 +19396,33 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.714457126570444,174.53774021999195</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.71456404342296,174.53862795505935</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-35.71436726248121,174.53944328575025</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
